--- a/artfynd/A 26670-2022 artfynd.xlsx
+++ b/artfynd/A 26670-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26670-2022 artfynd.xlsx
+++ b/artfynd/A 26670-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103221633</v>
+        <v>103221558</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>756413.0702235132</v>
+        <v>756572</v>
       </c>
       <c r="R2" t="n">
-        <v>7489426.494586426</v>
+        <v>7489265</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +747,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103221677</v>
+        <v>103221655</v>
       </c>
       <c r="B3" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>756507.9850763003</v>
+        <v>756422</v>
       </c>
       <c r="R3" t="n">
-        <v>7489669.705242439</v>
+        <v>7489582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +848,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103221566</v>
+        <v>103221690</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756738.0041566335</v>
+        <v>756636</v>
       </c>
       <c r="R4" t="n">
-        <v>7489353.931899874</v>
+        <v>7489683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +949,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103221587</v>
+        <v>103221638</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,31 +990,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756708.9981499321</v>
+        <v>756445</v>
       </c>
       <c r="R5" t="n">
-        <v>7489349.571610433</v>
+        <v>7489444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,32 +1050,18 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103221558</v>
+        <v>103221643</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,27 +1091,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756572.3974625663</v>
+        <v>756416</v>
       </c>
       <c r="R6" t="n">
-        <v>7489264.763324435</v>
+        <v>7489446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,19 +1151,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103221690</v>
+        <v>103221672</v>
       </c>
       <c r="B7" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1308,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756635.6756269928</v>
+        <v>756443</v>
       </c>
       <c r="R7" t="n">
-        <v>7489682.469657204</v>
+        <v>7489597</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,19 +1252,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,37 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103221643</v>
+        <v>103221566</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1424,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>756415.8545290208</v>
+        <v>756738</v>
       </c>
       <c r="R8" t="n">
-        <v>7489445.718253806</v>
+        <v>7489354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,19 +1353,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,37 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103221638</v>
+        <v>103221677</v>
       </c>
       <c r="B9" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5685</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1540,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>756445.0699919857</v>
+        <v>756508</v>
       </c>
       <c r="R9" t="n">
-        <v>7489443.906615087</v>
+        <v>7489670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,19 +1454,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,15 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103221651</v>
+        <v>103221633</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,31 +1495,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1661,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>756406.4631959966</v>
+        <v>756413</v>
       </c>
       <c r="R10" t="n">
-        <v>7489566.652288314</v>
+        <v>7489427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,32 +1555,18 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1738,15 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103221655</v>
+        <v>103221587</v>
       </c>
       <c r="B11" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,26 +1596,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1781,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>756422.0415318997</v>
+        <v>756709</v>
       </c>
       <c r="R11" t="n">
-        <v>7489581.699230187</v>
+        <v>7489350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,19 +1661,14 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1677,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1854,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103221685</v>
+        <v>103221651</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>756571.5692605437</v>
+        <v>756406</v>
       </c>
       <c r="R12" t="n">
-        <v>7489696.754343556</v>
+        <v>7489567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,19 +1771,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1979,42 +1805,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103221672</v>
+        <v>103221685</v>
       </c>
       <c r="B13" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2022,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>756443.0269074854</v>
+        <v>756571</v>
       </c>
       <c r="R13" t="n">
-        <v>7489596.883263953</v>
+        <v>7489697</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,19 +1881,14 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,7 +1897,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2098,12 +1918,7 @@
         <v>103221602</v>
       </c>
       <c r="B14" t="n">
-        <v>56542</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>756691.0283164846</v>
+        <v>756691</v>
       </c>
       <c r="R14" t="n">
-        <v>7489367.170859009</v>
+        <v>7489367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,19 +1991,9 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,6 +2017,115 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103221628</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jollegis, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>756498</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7489368</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26670-2022 artfynd.xlsx
+++ b/artfynd/A 26670-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221558</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221690</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221638</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221643</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221672</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221566</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221677</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221633</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221587</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221651</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221685</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221602</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2126,8 +2196,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103221628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>